--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F5D64F-AC29-4464-B5C0-2890C60DE783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EF7719-FD2A-4D70-BCB5-55AA82A44D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -418,21 +418,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -441,7 +441,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -449,7 +449,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -457,7 +457,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -465,21 +465,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -492,7 +492,7 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -512,7 +512,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5605,39 +5605,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5689,7 +5689,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -5800,13 +5800,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -5815,6 +5808,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -5879,11 +5879,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6396,7 +6416,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -6904,7 +6924,7 @@
       </c>
     </row>
     <row r="27" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -7135,7 +7155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
         <v>~TFM_INS-TS: region=POL; attribute=flo_cost;pset_pn=-IMP*Z</v>
@@ -18140,8 +18160,8 @@
       <c r="D257">
         <v>34</v>
       </c>
-      <c r="E257">
-        <v>65535</v>
+      <c r="E257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F257">
         <v>2.42</v>
@@ -18149,8 +18169,8 @@
       <c r="H257">
         <v>1.18</v>
       </c>
-      <c r="I257">
-        <v>65535</v>
+      <c r="I257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J257">
         <v>2.0099999999999998</v>
@@ -18178,8 +18198,8 @@
       <c r="D258">
         <v>34</v>
       </c>
-      <c r="E258">
-        <v>65535</v>
+      <c r="E258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F258">
         <v>3.1</v>
@@ -18187,8 +18207,8 @@
       <c r="H258">
         <v>1.71</v>
       </c>
-      <c r="I258">
-        <v>65535</v>
+      <c r="I258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J258">
         <v>2.38</v>
@@ -18216,8 +18236,8 @@
       <c r="D259">
         <v>34</v>
       </c>
-      <c r="E259">
-        <v>65535</v>
+      <c r="E259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F259">
         <v>3.54</v>
@@ -18225,8 +18245,8 @@
       <c r="H259">
         <v>1.91</v>
       </c>
-      <c r="I259">
-        <v>65535</v>
+      <c r="I259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J259">
         <v>2.66</v>
@@ -18254,8 +18274,8 @@
       <c r="D260">
         <v>34</v>
       </c>
-      <c r="E260">
-        <v>65535</v>
+      <c r="E260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F260">
         <v>4.0999999999999996</v>
@@ -18263,8 +18283,8 @@
       <c r="H260">
         <v>2.27</v>
       </c>
-      <c r="I260">
-        <v>65535</v>
+      <c r="I260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J260">
         <v>2.96</v>
@@ -18292,8 +18312,8 @@
       <c r="D261">
         <v>34</v>
       </c>
-      <c r="E261">
-        <v>65535</v>
+      <c r="E261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F261">
         <v>3.86</v>
@@ -18301,8 +18321,8 @@
       <c r="H261">
         <v>2.54</v>
       </c>
-      <c r="I261">
-        <v>65535</v>
+      <c r="I261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J261">
         <v>3.3</v>
@@ -18330,8 +18350,8 @@
       <c r="D262">
         <v>34</v>
       </c>
-      <c r="E262">
-        <v>65535</v>
+      <c r="E262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F262">
         <v>3.59</v>
@@ -18339,8 +18359,8 @@
       <c r="H262">
         <v>2.73</v>
       </c>
-      <c r="I262">
-        <v>65535</v>
+      <c r="I262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J262">
         <v>3.07</v>
@@ -18409,8 +18429,8 @@
       <c r="D264">
         <v>44</v>
       </c>
-      <c r="E264">
-        <v>65535</v>
+      <c r="E264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F264">
         <v>1.22</v>
@@ -18418,8 +18438,8 @@
       <c r="H264">
         <v>0</v>
       </c>
-      <c r="I264">
-        <v>65535</v>
+      <c r="I264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J264">
         <v>1.1299999999999999</v>
@@ -18447,8 +18467,8 @@
       <c r="D265">
         <v>44</v>
       </c>
-      <c r="E265">
-        <v>65535</v>
+      <c r="E265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F265">
         <v>1.5</v>
@@ -18456,8 +18476,8 @@
       <c r="H265">
         <v>0</v>
       </c>
-      <c r="I265">
-        <v>65535</v>
+      <c r="I265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J265">
         <v>1.31</v>
@@ -18485,8 +18505,8 @@
       <c r="D266">
         <v>44</v>
       </c>
-      <c r="E266">
-        <v>65535</v>
+      <c r="E266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F266">
         <v>2.12</v>
@@ -18494,8 +18514,8 @@
       <c r="H266">
         <v>0</v>
       </c>
-      <c r="I266">
-        <v>65535</v>
+      <c r="I266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J266">
         <v>1.68</v>
@@ -18523,8 +18543,8 @@
       <c r="D267">
         <v>44</v>
       </c>
-      <c r="E267">
-        <v>65535</v>
+      <c r="E267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F267">
         <v>2.5</v>
@@ -18532,8 +18552,8 @@
       <c r="H267">
         <v>0</v>
       </c>
-      <c r="I267">
-        <v>65535</v>
+      <c r="I267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J267">
         <v>2</v>
@@ -18561,8 +18581,8 @@
       <c r="D268">
         <v>44</v>
       </c>
-      <c r="E268">
-        <v>65535</v>
+      <c r="E268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F268">
         <v>2.79</v>
@@ -18570,8 +18590,8 @@
       <c r="H268">
         <v>0</v>
       </c>
-      <c r="I268">
-        <v>65535</v>
+      <c r="I268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J268">
         <v>2.08</v>
@@ -18599,8 +18619,8 @@
       <c r="D269">
         <v>44</v>
       </c>
-      <c r="E269">
-        <v>65535</v>
+      <c r="E269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F269">
         <v>2.95</v>
@@ -18608,8 +18628,8 @@
       <c r="H269">
         <v>0</v>
       </c>
-      <c r="I269">
-        <v>65535</v>
+      <c r="I269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J269">
         <v>2.4900000000000002</v>
@@ -18678,8 +18698,8 @@
       <c r="D271">
         <v>112</v>
       </c>
-      <c r="E271">
-        <v>65535</v>
+      <c r="E271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F271">
         <v>1.41</v>
@@ -18687,8 +18707,8 @@
       <c r="H271">
         <v>0.98</v>
       </c>
-      <c r="I271">
-        <v>65535</v>
+      <c r="I271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J271">
         <v>1.23</v>
@@ -18716,8 +18736,8 @@
       <c r="D272">
         <v>112</v>
       </c>
-      <c r="E272">
-        <v>65535</v>
+      <c r="E272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F272">
         <v>2.04</v>
@@ -18725,8 +18745,8 @@
       <c r="H272">
         <v>1.05</v>
       </c>
-      <c r="I272">
-        <v>65535</v>
+      <c r="I272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J272">
         <v>1.52</v>
@@ -18754,8 +18774,8 @@
       <c r="D273">
         <v>112</v>
       </c>
-      <c r="E273">
-        <v>65535</v>
+      <c r="E273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F273">
         <v>2.4</v>
@@ -18763,8 +18783,8 @@
       <c r="H273">
         <v>1.05</v>
       </c>
-      <c r="I273">
-        <v>65535</v>
+      <c r="I273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J273">
         <v>1.71</v>
@@ -18792,8 +18812,8 @@
       <c r="D274">
         <v>112</v>
       </c>
-      <c r="E274">
-        <v>65535</v>
+      <c r="E274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F274">
         <v>2.6</v>
@@ -18801,8 +18821,8 @@
       <c r="H274">
         <v>1.06</v>
       </c>
-      <c r="I274">
-        <v>65535</v>
+      <c r="I274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J274">
         <v>1.85</v>
@@ -18830,8 +18850,8 @@
       <c r="D275">
         <v>112</v>
       </c>
-      <c r="E275">
-        <v>65535</v>
+      <c r="E275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F275">
         <v>2.85</v>
@@ -18839,8 +18859,8 @@
       <c r="H275">
         <v>1.08</v>
       </c>
-      <c r="I275">
-        <v>65535</v>
+      <c r="I275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J275">
         <v>2</v>
@@ -18868,8 +18888,8 @@
       <c r="D276">
         <v>112</v>
       </c>
-      <c r="E276">
-        <v>65535</v>
+      <c r="E276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F276">
         <v>2.97</v>
@@ -18877,8 +18897,8 @@
       <c r="H276">
         <v>0</v>
       </c>
-      <c r="I276">
-        <v>65535</v>
+      <c r="I276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J276">
         <v>2.15</v>
@@ -19521,8 +19541,8 @@
       <c r="D292">
         <v>50</v>
       </c>
-      <c r="E292">
-        <v>65535</v>
+      <c r="E292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F292">
         <v>1.1000000000000001</v>
@@ -19530,8 +19550,8 @@
       <c r="H292">
         <v>-4.33</v>
       </c>
-      <c r="I292">
-        <v>65535</v>
+      <c r="I292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J292">
         <v>0.81</v>
@@ -19559,8 +19579,8 @@
       <c r="D293">
         <v>50</v>
       </c>
-      <c r="E293">
-        <v>65535</v>
+      <c r="E293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F293">
         <v>1.77</v>
@@ -19568,8 +19588,8 @@
       <c r="H293">
         <v>-6.1</v>
       </c>
-      <c r="I293">
-        <v>65535</v>
+      <c r="I293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J293">
         <v>1.27</v>
@@ -19597,8 +19617,8 @@
       <c r="D294">
         <v>50</v>
       </c>
-      <c r="E294">
-        <v>65535</v>
+      <c r="E294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F294">
         <v>1.87</v>
@@ -19606,8 +19626,8 @@
       <c r="H294">
         <v>-6.86</v>
       </c>
-      <c r="I294">
-        <v>65535</v>
+      <c r="I294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J294">
         <v>1.1499999999999999</v>
@@ -19635,8 +19655,8 @@
       <c r="D295">
         <v>50</v>
       </c>
-      <c r="E295">
-        <v>65535</v>
+      <c r="E295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F295">
         <v>1.96</v>
@@ -19644,8 +19664,8 @@
       <c r="H295">
         <v>-9.2100000000000009</v>
       </c>
-      <c r="I295">
-        <v>65535</v>
+      <c r="I295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J295">
         <v>1.31</v>
@@ -19673,8 +19693,8 @@
       <c r="D296">
         <v>50</v>
       </c>
-      <c r="E296">
-        <v>65535</v>
+      <c r="E296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F296">
         <v>2.13</v>
@@ -19682,8 +19702,8 @@
       <c r="H296">
         <v>-6.95</v>
       </c>
-      <c r="I296">
-        <v>65535</v>
+      <c r="I296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J296">
         <v>1.6</v>
@@ -19711,8 +19731,8 @@
       <c r="D297">
         <v>50</v>
       </c>
-      <c r="E297">
-        <v>65535</v>
+      <c r="E297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F297">
         <v>2</v>
@@ -19720,8 +19740,8 @@
       <c r="H297">
         <v>-10.07</v>
       </c>
-      <c r="I297">
-        <v>65535</v>
+      <c r="I297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J297">
         <v>1.55</v>
@@ -19790,8 +19810,8 @@
       <c r="D299">
         <v>52</v>
       </c>
-      <c r="E299">
-        <v>65535</v>
+      <c r="E299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F299">
         <v>0.61</v>
@@ -19799,8 +19819,8 @@
       <c r="H299">
         <v>0</v>
       </c>
-      <c r="I299">
-        <v>65535</v>
+      <c r="I299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J299">
         <v>0.53</v>
@@ -19828,8 +19848,8 @@
       <c r="D300">
         <v>63</v>
       </c>
-      <c r="E300">
-        <v>65535</v>
+      <c r="E300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F300">
         <v>1.07</v>
@@ -19837,8 +19857,8 @@
       <c r="H300">
         <v>0</v>
       </c>
-      <c r="I300">
-        <v>65535</v>
+      <c r="I300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J300">
         <v>0.6</v>
@@ -19866,8 +19886,8 @@
       <c r="D301">
         <v>52</v>
       </c>
-      <c r="E301">
-        <v>65535</v>
+      <c r="E301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F301">
         <v>1.0900000000000001</v>
@@ -19875,8 +19895,8 @@
       <c r="H301">
         <v>0</v>
       </c>
-      <c r="I301">
-        <v>65535</v>
+      <c r="I301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J301">
         <v>0.6</v>
@@ -19904,8 +19924,8 @@
       <c r="D302">
         <v>63</v>
       </c>
-      <c r="E302">
-        <v>65535</v>
+      <c r="E302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F302">
         <v>1.25</v>
@@ -19913,8 +19933,8 @@
       <c r="H302">
         <v>0</v>
       </c>
-      <c r="I302">
-        <v>65535</v>
+      <c r="I302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J302">
         <v>0.87</v>
@@ -19942,8 +19962,8 @@
       <c r="D303">
         <v>52</v>
       </c>
-      <c r="E303">
-        <v>65535</v>
+      <c r="E303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F303">
         <v>1.35</v>
@@ -19951,8 +19971,8 @@
       <c r="H303">
         <v>0</v>
       </c>
-      <c r="I303">
-        <v>65535</v>
+      <c r="I303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J303">
         <v>0.78</v>
@@ -19980,8 +20000,8 @@
       <c r="D304">
         <v>63</v>
       </c>
-      <c r="E304">
-        <v>65535</v>
+      <c r="E304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F304">
         <v>1.62</v>
@@ -19989,8 +20009,8 @@
       <c r="H304">
         <v>-2.31</v>
       </c>
-      <c r="I304">
-        <v>65535</v>
+      <c r="I304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J304">
         <v>0.61</v>
@@ -20059,8 +20079,8 @@
       <c r="D306">
         <v>163</v>
       </c>
-      <c r="E306">
-        <v>65535</v>
+      <c r="E306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F306">
         <v>0.75</v>
@@ -20068,8 +20088,8 @@
       <c r="H306">
         <v>0.46</v>
       </c>
-      <c r="I306">
-        <v>65535</v>
+      <c r="I306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J306">
         <v>0.54</v>
@@ -20097,8 +20117,8 @@
       <c r="D307">
         <v>166</v>
       </c>
-      <c r="E307">
-        <v>65535</v>
+      <c r="E307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F307">
         <v>1.1499999999999999</v>
@@ -20106,8 +20126,8 @@
       <c r="H307">
         <v>0.51</v>
       </c>
-      <c r="I307">
-        <v>65535</v>
+      <c r="I307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J307">
         <v>0.74</v>
@@ -20135,8 +20155,8 @@
       <c r="D308">
         <v>163</v>
       </c>
-      <c r="E308">
-        <v>65535</v>
+      <c r="E308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F308">
         <v>1.21</v>
@@ -20144,8 +20164,8 @@
       <c r="H308">
         <v>-0.95</v>
       </c>
-      <c r="I308">
-        <v>65535</v>
+      <c r="I308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J308">
         <v>0.88</v>
@@ -20173,8 +20193,8 @@
       <c r="D309">
         <v>166</v>
       </c>
-      <c r="E309">
-        <v>65535</v>
+      <c r="E309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F309">
         <v>1.28</v>
@@ -20182,8 +20202,8 @@
       <c r="H309">
         <v>-1.8</v>
       </c>
-      <c r="I309">
-        <v>65535</v>
+      <c r="I309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J309">
         <v>0.89</v>
@@ -20211,8 +20231,8 @@
       <c r="D310">
         <v>163</v>
       </c>
-      <c r="E310">
-        <v>65535</v>
+      <c r="E310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F310">
         <v>1.48</v>
@@ -20220,8 +20240,8 @@
       <c r="H310">
         <v>-5.93</v>
       </c>
-      <c r="I310">
-        <v>65535</v>
+      <c r="I310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J310">
         <v>1.08</v>
@@ -20249,8 +20269,8 @@
       <c r="D311">
         <v>166</v>
       </c>
-      <c r="E311">
-        <v>65535</v>
+      <c r="E311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F311">
         <v>1.59</v>
@@ -20258,8 +20278,8 @@
       <c r="H311">
         <v>-5.35</v>
       </c>
-      <c r="I311">
-        <v>65535</v>
+      <c r="I311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J311">
         <v>0.97</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EF7719-FD2A-4D70-BCB5-55AA82A44D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25246A7C-B655-4E72-BE12-3D83470716C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25246A7C-B655-4E72-BE12-3D83470716C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAD29CF-37D6-4197-99B9-7EED0919BFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAD29CF-37D6-4197-99B9-7EED0919BFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CA920C-0388-4FED-A78F-FED9ACB4B78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CA920C-0388-4FED-A78F-FED9ACB4B78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D60EFBD-B462-4F8C-B984-22F9B1C50A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D60EFBD-B462-4F8C-B984-22F9B1C50A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614ADB42-3F22-4961-AA96-B7671368E004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614ADB42-3F22-4961-AA96-B7671368E004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FCE528-3D6C-420D-B8D0-B9A6A40A23D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FCE528-3D6C-420D-B8D0-B9A6A40A23D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD2A50D-8AF1-400A-9EF7-D2F3EBC1893D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD2A50D-8AF1-400A-9EF7-D2F3EBC1893D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E605DC35-F57F-4E0C-B71A-31BD61A0D112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E605DC35-F57F-4E0C-B71A-31BD61A0D112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2786C3-DED3-4484-826C-BCECC95DA6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
